--- a/employee_surveys/046_work_from_home_setup_poll--employee_surveys.xlsx
+++ b/employee_surveys/046_work_from_home_setup_poll--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'development'}</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Development'}</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Customer Service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mac'}</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mac'}</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mon-fri,_8-5'}</t>
+          <t>mon-fri,_8-5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mon-Fri, 8-5'}</t>
+          <t>Mon-Fri, 8-5</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mon-fri,_9-6'}</t>
+          <t>mon-fri,_9-6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mon-Fri, 9-6'}</t>
+          <t>Mon-Fri, 9-6</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mon-thu,_8-4'}</t>
+          <t>mon-thu,_8-4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mon-Thu, 8-4'}</t>
+          <t>Mon-Thu, 8-4</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mon-thu,_9-5'}</t>
+          <t>mon-thu,_9-5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mon-Thu, 9-5'}</t>
+          <t>Mon-Thu, 9-5</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"yes,_it's_a_dedicated_space"}</t>
+          <t>yes,_it's_a_dedicated_space</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "Yes, it's a dedicated space"}</t>
+          <t>Yes, it's a dedicated space</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'no,_i_work_from_anywhere'}</t>
+          <t>no,_i_work_from_anywhere</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'No, I work from anywhere'}</t>
+          <t>No, I work from anywhere</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sometimes,_it_depends_on_the_day'}</t>
+          <t>sometimes,_it_depends_on_the_day</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sometimes, it depends on the day'}</t>
+          <t>Sometimes, it depends on the day</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'use_video_conferencing_software'}</t>
+          <t>use_video_conferencing_software</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Use video conferencing software'}</t>
+          <t>Use video conferencing software</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email_or_text'}</t>
+          <t>email_or_text</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email or text'}</t>
+          <t>Email or text</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes,_frequently'}</t>
+          <t>yes,_frequently</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes, frequently'}</t>
+          <t>Yes, frequently</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'yes,_rarely'}</t>
+          <t>yes,_rarely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Yes, rarely'}</t>
+          <t>Yes, rarely</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'regular_video_calls'}</t>
+          <t>regular_video_calls</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Regular video calls'}</t>
+          <t>Regular video calls</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email_and_instant_messaging'}</t>
+          <t>email_and_instant_messaging</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email and instant messaging'}</t>
+          <t>Email and instant messaging</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-person_meetings'}</t>
+          <t>in-person_meetings</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-person meetings'}</t>
+          <t>In-person meetings</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'no,_it_depends_on_the_day'}</t>
+          <t>no,_it_depends_on_the_day</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'No, it depends on the day'}</t>
+          <t>No, it depends on the day</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'difficulty_staying_connected_with_team'}</t>
+          <t>difficulty_staying_connected_with_team</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Difficulty staying connected with team'}</t>
+          <t>Difficulty staying connected with team</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'difficulty_with_time_zone_challenges'}</t>
+          <t>difficulty_with_time_zone_challenges</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Difficulty with time zone challenges'}</t>
+          <t>Difficulty with time zone challenges</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'difficulty_with_technology_integration'}</t>
+          <t>difficulty_with_technology_integration</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Difficulty with technology integration'}</t>
+          <t>Difficulty with technology integration</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'difficulty_with_communication_challenges'}</t>
+          <t>difficulty_with_communication_challenges</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Difficulty with communication challenges'}</t>
+          <t>Difficulty with communication challenges</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cable_internet'}</t>
+          <t>cable_internet</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cable internet'}</t>
+          <t>Cable internet</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'wi-fi'}</t>
+          <t>wi-fi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Wi-Fi'}</t>
+          <t>Wi-Fi</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'alone'}</t>
+          <t>alone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Alone'}</t>
+          <t>Alone</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2-3_people'}</t>
+          <t>2-3_people</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2-3 people'}</t>
+          <t>2-3 people</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'4_or_more_people'}</t>
+          <t>4_or_more_people</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '4 or more people'}</t>
+          <t>4 or more people</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'every_few_hours'}</t>
+          <t>every_few_hours</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Every few hours'}</t>
+          <t>Every few hours</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'several_times_a_day'}</t>
+          <t>several_times_a_day</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Several times a day'}</t>
+          <t>Several times a day</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'most_days'}</t>
+          <t>most_days</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Most days'}</t>
+          <t>Most days</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'few_days_a_week'}</t>
+          <t>few_days_a_week</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Few days a week'}</t>
+          <t>Few days a week</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
